--- a/5/search/FY2_Missile2_results/solutions_direction_225.0.xlsx
+++ b/5/search/FY2_Missile2_results/solutions_direction_225.0.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,107 +487,317 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>225</v>
+        <v>193.5</v>
       </c>
       <c r="B2" t="n">
-        <v>81.2</v>
+        <v>140</v>
       </c>
       <c r="C2" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E2" t="n">
-        <v>11310.99515241183</v>
+        <v>8732.837067463806</v>
       </c>
       <c r="F2" t="n">
-        <v>710.995152411828</v>
+        <v>615.6235774441582</v>
       </c>
       <c r="G2" t="n">
         <v>1400</v>
       </c>
       <c r="H2" t="n">
-        <v>10966.49272861774</v>
+        <v>7235.387390051385</v>
       </c>
       <c r="I2" t="n">
-        <v>366.492728617742</v>
+        <v>256.117717106064</v>
       </c>
       <c r="J2" t="n">
-        <v>1223.6</v>
+        <v>807.0999999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>3.300000000000001</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>225</v>
+        <v>211.5</v>
       </c>
       <c r="B3" t="n">
-        <v>100.8</v>
+        <v>106</v>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E3" t="n">
-        <v>11429.78909165117</v>
+        <v>10915.4417109416</v>
       </c>
       <c r="F3" t="n">
-        <v>829.7890916511682</v>
+        <v>735.3818256813132</v>
       </c>
       <c r="G3" t="n">
         <v>1400</v>
       </c>
       <c r="H3" t="n">
-        <v>11002.13091038954</v>
+        <v>10282.78270899086</v>
       </c>
       <c r="I3" t="n">
-        <v>402.1309103895443</v>
+        <v>347.6878906620793</v>
       </c>
       <c r="J3" t="n">
-        <v>1223.6</v>
+        <v>1159.9</v>
       </c>
       <c r="K3" t="n">
-        <v>1.700000000000001</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>225</v>
+        <v>211.5</v>
       </c>
       <c r="B4" t="n">
-        <v>140</v>
+        <v>108</v>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E4" t="n">
-        <v>11604.02020253553</v>
+        <v>10894.9783469971</v>
       </c>
       <c r="F4" t="n">
-        <v>1004.020202535533</v>
+        <v>722.8418601281305</v>
       </c>
       <c r="G4" t="n">
         <v>1400</v>
       </c>
       <c r="H4" t="n">
+        <v>10250.3823827454</v>
+      </c>
+      <c r="I4" t="n">
+        <v>327.8329452028733</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1159.9</v>
+      </c>
+      <c r="K4" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>211.5</v>
+      </c>
+      <c r="B5" t="n">
+        <v>132</v>
+      </c>
+      <c r="C5" t="n">
+        <v>8</v>
+      </c>
+      <c r="D5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E5" t="n">
+        <v>11099.61198644208</v>
+      </c>
+      <c r="F5" t="n">
+        <v>848.2415156599582</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H5" t="n">
+        <v>10311.7724745789</v>
+      </c>
+      <c r="I5" t="n">
+        <v>365.4528418624216</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1159.9</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>211.5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>134</v>
+      </c>
+      <c r="C6" t="n">
+        <v>8</v>
+      </c>
+      <c r="D6" t="n">
+        <v>7</v>
+      </c>
+      <c r="E6" t="n">
+        <v>11085.96974381241</v>
+      </c>
+      <c r="F6" t="n">
+        <v>839.881538624503</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H6" t="n">
+        <v>10286.19326964827</v>
+      </c>
+      <c r="I6" t="n">
+        <v>349.7778849209432</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1159.9</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>220.5</v>
+      </c>
+      <c r="B7" t="n">
+        <v>114</v>
+      </c>
+      <c r="C7" t="n">
+        <v>8</v>
+      </c>
+      <c r="D7" t="n">
+        <v>6</v>
+      </c>
+      <c r="E7" t="n">
+        <v>11306.50975937277</v>
+      </c>
+      <c r="F7" t="n">
+        <v>807.7033799228726</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H7" t="n">
+        <v>10786.39207890235</v>
+      </c>
+      <c r="I7" t="n">
+        <v>363.4809148650271</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1223.6</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>220.5</v>
+      </c>
+      <c r="B8" t="n">
+        <v>116</v>
+      </c>
+      <c r="C8" t="n">
+        <v>8</v>
+      </c>
+      <c r="D8" t="n">
+        <v>6</v>
+      </c>
+      <c r="E8" t="n">
+        <v>11294.34326392317</v>
+      </c>
+      <c r="F8" t="n">
+        <v>797.3122111495896</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H8" t="n">
+        <v>10765.10071186555</v>
+      </c>
+      <c r="I8" t="n">
+        <v>345.2963695117819</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1223.6</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>225</v>
+      </c>
+      <c r="B9" t="n">
+        <v>102</v>
+      </c>
+      <c r="C9" t="n">
+        <v>8</v>
+      </c>
+      <c r="D9" t="n">
+        <v>6</v>
+      </c>
+      <c r="E9" t="n">
+        <v>11423.00086655178</v>
+      </c>
+      <c r="F9" t="n">
+        <v>823.0008665517772</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H9" t="n">
+        <v>10990.25151646561</v>
+      </c>
+      <c r="I9" t="n">
+        <v>390.2515164656102</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1223.6</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>225</v>
+      </c>
+      <c r="B10" t="n">
+        <v>140</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>6</v>
+      </c>
+      <c r="E10" t="n">
+        <v>11604.02020253553</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1004.020202535533</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H10" t="n">
         <v>11010.05050633883</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I10" t="n">
         <v>410.0505063388335</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J10" t="n">
         <v>1223.6</v>
       </c>
-      <c r="K4" t="n">
-        <v>2.600000000000001</v>
+      <c r="K10" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
